--- a/backend/scripts/data/Business_Model_Assessments.xlsx
+++ b/backend/scripts/data/Business_Model_Assessments.xlsx
@@ -1512,7 +1512,7 @@
         <v>33.33</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>33.33</v>
+        <v>33.34</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>33.33</v>
@@ -1521,7 +1521,7 @@
         <v>33.33</v>
       </c>
       <c r="U9" s="9" t="n">
-        <v>33.33</v>
+        <v>33.34</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>50</v>
